--- a/important_mails_2026-04-09.xlsx
+++ b/important_mails_2026-04-09.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,314 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
+          <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
+          <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+ We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
+ Please note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. In this case, we may continue to attempt charging your card until the remaining balance in your Amazon Selling on Amazon payment account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For details, refer “Making a Payment” in Seller Central Help.
+ To view your payment activity anytime, please log in to your account and refer the Payments Report page.
+ Thank you for selling on Amazon.
+ Amazon Payments UK Limited
+Amazon Payments UK Limited, a private company limited by shares, is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60) with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom. Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
+ Was this e-mail helpful?
+ SPC-EUAmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Reactivate your EU listings - GPSR compliance required</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Reactivate your EU listings - GPSR compliance required
+ Hello Weihai EU,
+ Some of your listings have been deactivated from our European Union (EU) stores due to missing compliance information. This action does not impact your account health.
+ You can find examples of your deactivated listings at the bottom of this email, and the full list on your Account Health page. Review the affected listings and next steps to meet General Product Safety Regulation (GPSR) requirements below.
+ Submit compliance information
+ Submit compliance information
+ How do I reactivate my listings?
+ To reactivate your listings, provide the required GPSR compliance information by following the instructions below:
+-
+ Go to your Account Health page .
+- Select 'Add filters' and check 'Listing removed' in the "Filter by action taken" column.
+- Click 'Submit' next to the deactivated listing and follow the instructions provided.
+- Follow the steps on Suppressed listings to resolve any outstanding listing issues. Existing issues prevent listings from being reactivated, even if you’ve fulfilled all compliance requirements.
+ Note: If you’ve recently submitted information on your Account Health page, and no longer </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.ca
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 3/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate nei nostri negozi dell'Unione europea a causa della mancanza di informazioni relative alla conformità. Questa azione non avrà alcun impatto sullo stato del tuo account.
+ Puoi trovare esempi delle tue offerte disattivate in fondo a questa e-mail e l'elenco completo nella pagina Stato dell'account. Rivedi le offerte interessate e i passaggi successivi per soddisfare i requisiti del Regolamento sulla sicurezza generale dei prodotti riportati di seguito.
+ Inviare le informazioni sulla conformità
+ Inviare le informazioni sulla conformità
+ Come faccio a riattivare le mie offerte?
+ Per riattivare le offerte, fornisci le informazioni richieste relative alla conformità al regolamento sulla sicurezza generale dei prodotti seguendo le istruzioni riportate di seguito:
+-
+ Vai alla pagina Stato dell'account .
+- Seleziona "Aggiungi filtri" e quindi "Offerta rimossa" nella colonna "Filtra per azione intrapresa".
+- Clicca su "Invia" accanto all'offerta disattivata e segui le istruzioni fornite.
+- Segui la procedura indi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
+ Hola:
+ Con entrada en vigor el 1 de mayo de 2026, las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición. Con esta actualización, seguimos los estándares del sector y te proporcionamos más visibilidad sobre tus actividades de retirada y puesta de inventario a nuestra disposición.
+ Este cambio sólo afecta al momento en que se te cobra. No hay cambios en las tarifas por retirada y puesta de inventario a disposición de Amazon. Antes, estas tarifas se cobraban una vez que se completaba toda la solicitud de retirada o puesta de inventario a disposición de Amazon.
+ No es necesario que hagas nada. Este cambio se aplicará automáticamente a las nuevas solicitudes de retirada y puesta de inventario a disposición de Amazon creadas a partir del 1 de mayo.
+ Para consultar los cargos por envío de las retiradas y puestas de inventario a nuestra disposición y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
+ Dzień dobry,
+ od 1 maja 2026 r. opłaty za wycofanie i usunięcie w ramach usługi Realizacja przez Amazon (FBA) będą pobierane od każdej jednostki w momencie jej wycofania lub usunięcia. Aktualizacja jest zgodna ze standardami branżowymi i zapewnia większą przejrzystość działań związanych z wycofywaniem i usuwaniem zapasów.
+ Zmiana dotyczy wyłącznie momentu pobrania opłaty. Stawki opłat za wycofanie i usunięcie zapasów pozostają bez zmian. Wcześniej opłaty były pobierane po zakończeniu realizacji całego zlecenia wycofania zapasów lub zlecenia usunięcia zapasów.
+ Nie musisz podejmować żadnych działań. Zmiana zostanie automatycznie zastosowana do nowych zleceń wycofania zapasów i zleceń usunięcia zapasów utworzonych od 1 maja.
+ Aby sprawdzić opłaty na poziomie przesyłki dotyczące wycofania i usunięcia zapasów oraz terminy wycofywania jednostek, przejdź na kartę Transakcje .
+ Więcej informacji znajdziesz na stronie Aktualizacje opłat za wycofanie i usunięcie zapasów w ramach FBA .
+ Zespół Amazon Europe
+ Zgłoś problem z tym e-mailem
+ Jeśli masz pytani</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -526,39 +819,142 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>FBA removal and disposal fees to be charged as units are processed</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>96
+ FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
+ Hello,
+ Effective May 1, 2026, Fulfillment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
+ This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
+ No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
+ To review your removal and disposal shipment level charges and when units are removed, go to Transaction view .
+ For more information, go to FBA Removal and Disposal fee updates .
+ The Amazon Europe team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon EU S.à r.l.
+38 avenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>FBA removal and disposal fees to be charged as units are processed</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>96
+ FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
+ Hello,
+ Effective as of May 1, 2026, Fulfilment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time that each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
+ This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
+ No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
+ To review your removal and disposal shipment-level charges and when units are removed, go to Transaction view .
+ For more information, go to FBA removal and disposal fee updates .
+ The Amazon Europe team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon EU S.à</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -584,39 +980,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -637,39 +1033,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -683,40 +1079,40 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -733,39 +1129,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -785,88 +1181,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 04/02/26 15:38 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 23,43.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éxi</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -887,39 +1234,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -940,40 +1287,40 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -989,39 +1336,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1036,39 +1383,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1080,39 +1427,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1124,39 +1471,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1168,39 +1515,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1212,39 +1559,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1256,39 +1603,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1300,39 +1647,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1344,39 +1691,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1388,39 +1735,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1432,39 +1779,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1483,39 +1830,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1527,39 +1874,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1571,39 +1918,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1615,39 +1962,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1659,39 +2006,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1703,39 +2050,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1747,39 +2094,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1791,39 +2138,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1842,39 +2189,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1886,40 +2233,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1938,39 +2285,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1982,39 +2329,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -2033,39 +2380,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -2097,39 +2444,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -2156,39 +2503,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -2200,123 +2547,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>96
- A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
- Hola:
- El aumento de los costes del combustible y logística ha incrementado los gastos operativos en todo el sector. Hasta ahora, hemos podido asimilar este aumento de costes. Sin embargo, al igual que otros transportistas importantes, cuando los costes se mantienen altos, aplicamos recargos temporales a nuestras tarifas de gestión logística para recuperar una parte de estos aumentos de costes.
- A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon del Reino Unido, Francia, Alemania, Italia, España, Polonia, Suecia, Países Bajos, Irlanda y Bélgica. A partir del 2 de mayo de 2026, este mismo recargo entrará en vigor para el servicio de Logística Multicanal en el Reino Unido, Francia, Alemania, Italia y España. Gracias al trabajo que hemos llevado a cabo juntos para reducir los costes, este recargo es considerablemente infer</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>96
- Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
- Dzień dobry,
- wzrost cen paliwa i transportu przyczynił się do zwiększenia kosztów operacyjnych w całej branży. Do tej pory pokrywaliśmy te zwiększone koszty. Jednak, ponieważ wzrost kosztów się utrzymuje, wprowadzamy tymczasowe dopłaty do opłat za realizację. Celem jest odzyskanie części zwiększonych kosztów rzeczywistych, które ponosimy. Podobne działania podejmują inni najważniejsi przewoźnicy.
- Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) w Zjednoczonym Królestwie, Francji, Niemczech, Włoszech, Hiszpanii, Polsce, Szwecji, Holandii, Irlandii i Belgii zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki . W przypadku usługi „Realizacja wielokanałowa” (MCF) w Zjednoczonym Królestwie, Francji, Niemczech, Włoszech i Hiszpanii dopłata ta będzie miała zastosowanie od 2 maja 2026 r. Dzięki wspólnym wysiłkom, jakie podjęliśmy już wcześnie</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -2329,39 +2592,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -2370,39 +2633,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2420,39 +2683,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2478,39 +2741,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2530,40 +2793,40 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2579,39 +2842,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2631,39 +2894,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2689,39 +2952,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2737,39 +3000,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2790,39 +3053,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -2836,40 +3099,40 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -2885,39 +3148,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2937,39 +3200,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2983,39 +3246,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3035,39 +3298,88 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 04/02/26 15:38 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 23,43.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éxi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -3090,39 +3402,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3142,39 +3454,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3191,39 +3503,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3240,39 +3552,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -3287,39 +3599,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3343,85 +3655,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Nieuregulowane saldo na koncie Amazon</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Witamy!
- Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
- Jeśli ta karta ma limit kredytowy, możemy ją obciążać do momentu pełnej spłaty nieuregulowanego salda.
- Aby uzyskać więcej informacji, wyszukaj Dokonaj płatności w Pomocy Seller Central.
- Aby dowiedzieć się więcej na temat raportów płatności i Twoich działań, wyszukaj Wyświetl moje raporty o płatnościach w Pomocy Seller Central.
- Z poważaniem,
- Amazon Payments Europe SCA (société en commandite par actions) to spółka komandytowo-akcyjna zarejestrowana w Luksemburgu, numer rejestracyjny (RCS Luxembourg) B 153 265, z siedzibą pod adresem 38 avenue J.F. Kennedy, L-1855 Luxembourg. Numer VAT: LU 24448288. Amazon Payments Europe SCA posiada upoważnienie Komisji Nadzoru Sektora Finansowego w Luksemburgu do emisji pieniądza elektronicznego (numer licencji 36/10)
- Czy ten e-mail był pomocny?
- SPC-EUAmazon-1037940607738415</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -3444,39 +3710,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3494,39 +3760,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3544,39 +3810,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3596,39 +3862,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3646,39 +3912,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3696,39 +3962,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3746,39 +4012,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3793,39 +4059,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3843,39 +4109,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3893,39 +4159,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3943,39 +4209,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3990,39 +4256,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4037,39 +4303,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4084,39 +4350,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4135,40 +4401,40 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -4187,39 +4453,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4229,39 +4495,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4279,39 +4545,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4327,39 +4593,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4378,39 +4644,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4428,39 +4694,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -4482,39 +4748,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -4537,39 +4803,123 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>96
+ A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
+ Hola:
+ El aumento de los costes del combustible y logística ha incrementado los gastos operativos en todo el sector. Hasta ahora, hemos podido asimilar este aumento de costes. Sin embargo, al igual que otros transportistas importantes, cuando los costes se mantienen altos, aplicamos recargos temporales a nuestras tarifas de gestión logística para recuperar una parte de estos aumentos de costes.
+ A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon del Reino Unido, Francia, Alemania, Italia, España, Polonia, Suecia, Países Bajos, Irlanda y Bélgica. A partir del 2 de mayo de 2026, este mismo recargo entrará en vigor para el servicio de Logística Multicanal en el Reino Unido, Francia, Alemania, Italia y España. Gracias al trabajo que hemos llevado a cabo juntos para reducir los costes, este recargo es considerablemente infer</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
+ Dzień dobry,
+ wzrost cen paliwa i transportu przyczynił się do zwiększenia kosztów operacyjnych w całej branży. Do tej pory pokrywaliśmy te zwiększone koszty. Jednak, ponieważ wzrost kosztów się utrzymuje, wprowadzamy tymczasowe dopłaty do opłat za realizację. Celem jest odzyskanie części zwiększonych kosztów rzeczywistych, które ponosimy. Podobne działania podejmują inni najważniejsi przewoźnicy.
+ Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) w Zjednoczonym Królestwie, Francji, Niemczech, Włoszech, Hiszpanii, Polsce, Szwecji, Holandii, Irlandii i Belgii zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki . W przypadku usługi „Realizacja wielokanałowa” (MCF) w Zjednoczonym Królestwie, Francji, Niemczech, Włoszech i Hiszpanii dopłata ta będzie miała zastosowanie od 2 maja 2026 r. Dzięki wspólnym wysiłkom, jakie podjęliśmy już wcześnie</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -4599,39 +4949,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -4649,39 +4999,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4698,39 +5048,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -4746,39 +5096,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -4807,39 +5157,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -4860,39 +5210,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4907,39 +5257,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -4953,40 +5303,40 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5002,39 +5352,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5050,39 +5400,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5098,39 +5448,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5146,40 +5496,40 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5195,39 +5545,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5245,39 +5595,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -5293,39 +5643,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5340,39 +5690,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -5387,39 +5737,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5440,40 +5790,40 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -5488,39 +5838,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -5541,39 +5891,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -5606,39 +5956,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5654,39 +6004,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5702,39 +6052,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5752,39 +6102,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5801,39 +6151,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -5857,39 +6207,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5904,39 +6254,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -5952,39 +6302,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6001,40 +6351,40 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6050,39 +6400,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -6102,39 +6452,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6150,40 +6500,40 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6199,88 +6549,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>春季促销日 2026：最后提报您促销活动的机会</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>立即规划您的促销
-尊敬的卖家：
-春季促销日已经开始！您仍然可以为高潜力商品提交 Prime专享价格折扣和优惠券。不要错过在此次春季购物活动中触达数百万顾客的最后机会。
-关键日期
-活动日期： 2026 年 3 月 10 - 16 日
-提交截止日期： 活动结束前 12 小时
-即刻提报您的促销活动
-优惠券 &gt; https://go.amazonsellerservices.com/e/229492/oupon-ld-DC-EM-D403389586-Wk11/7z24pyz/6548637104/h/o6MODTBWFOoJ-lTgG6jkhHwTY0UdhKXkfXm7u4fY9qo
-价格折扣 &gt;https://go.amazonsellerservices.com/e/229492/reate-ld-DC-EM-D403389586-Wk11/7z24pz3/6548637104/h/o6MODTBWFOoJ-lTgG6jkhHwTY0UdhKXkfXm7u4fY9qo
-您的 ASIN 推荐清单
-以下为您精选了一批适合提报春季促销日活动的推荐 ASIN。
-&lt;div style="padding: 0 20px; "&gt;&lt;table style="width:100%; border-collapse:collapse; text-align:center; font-family:Amazon Ember Display, Arial, sans-serif; border:2px solid #868D95; border-radius:10px 10px 0 0; overflow:hidden; "&gt;&lt;thead&gt;&lt;tr style="background-color:#dfdad5;"&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;站点&lt;/th&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;ASIN&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="padding:10px; border-top:2px solid #868D9</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6301,39 +6602,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6356,39 +6657,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6409,39 +6710,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6465,39 +6766,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6520,39 +6821,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6575,39 +6876,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6629,39 +6930,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -6691,39 +6992,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6739,39 +7040,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6787,40 +7088,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6839,40 +7140,40 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6890,39 +7191,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -6936,56 +7237,6 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>Atenda aos requisitos de conformidade em ofertas</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>96
-Ação necessária: Informações importantes sobre suas ofertas
- Estamos entrando em contato porque você publicou produtos que exigem o envio de documentos para verificação de conformidade.
- As ofertas estão sem os documentos de conformidade necessários
- Olá,
- Estamos entrando em contato porque você publicou produtos que exigem o envio de documentos para verificação de conformidade. Clique em Revisar requisitos de conformidade abaixo para acessar a lista de produtos afetados e enviar os documentos necessários. Se você não enviar os documentos até o prazo indicado para cada produto nesse link, poderemos excluir as ofertas afetadas.
- Revisar requisitos de conformidade
- A tabela abaixo contém uma amostra das ofertas afetadas. Clique em Revisar requisitos de conformidade para consultar todas as suas ofertas afetadas.
- SKU ASIN Status da oferta 7N-0PZT-LEBX B0FCDRNTT8 Em risco de remoção
- Por que isso está acontecendo?
-Essa exigência ajuda a garantir que os produtos estejam em conformidade com as leis locais e sejam seguros para os clientes.
- Como faço para continuar vendendo os produtos afetados?
-Clique em Revisar requisitos de conformidade para obter mais informações sobre os documento</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/important_mails_2026-04-09.xlsx
+++ b/important_mails_2026-04-09.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -599,21 +599,68 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
+          <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>donotreply@amazon.com</t>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
+          <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Store inventory at origin in China with lower costs and faster speeds.
+ Hello,
+ Starting April 9, 2026, you can store your inventory in bulk at a lower cost in our new Global Warehousing &amp; Distribution (GWD) facility in Shenzhen, China, and seamlessly replenish to our US fulfillment network when needed.
+ By using GWD in Shenzhen, you can:
+- Reduce storage costs by up to 45% compared to US Amazon Warehousing and Distribution (AWD).
+- Get inventory to US fulfillment centers up to seven days faster when paired with Amazon Global Logistics (AGL).
+- Maintain consistently healthy inventory levels through reliable, automated cross-border replenishment.
+- Choose your management style of either AI-powered automated replenishment or manual control while we handle the entire cross-border logistics process.
+- Streamline your supply chain of shipping, customs clearance, and delivery to our fulfillment centers all through a single, integrated solution. GWD is the first step in our Next Generation of Global Selling vision — where you list once, bring your inventory to the warehouse at origin, and sell it globally from day one. This vision transforms cross-border commerce: you focus on buildin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -632,39 +679,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -683,39 +730,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -727,39 +774,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -775,39 +822,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -819,39 +866,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -871,39 +918,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -922,39 +969,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -980,39 +1027,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1033,39 +1080,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -1079,40 +1126,40 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -1129,39 +1176,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1181,39 +1228,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -1234,39 +1281,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -1287,40 +1334,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -1336,39 +1383,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1383,39 +1430,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1427,39 +1474,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1471,39 +1518,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1515,39 +1562,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1559,39 +1606,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1603,39 +1650,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1647,39 +1694,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1691,39 +1738,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1735,39 +1782,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1779,39 +1826,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1830,39 +1877,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1874,39 +1921,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1918,39 +1965,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1962,39 +2009,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2006,39 +2053,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -2050,39 +2097,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -2094,39 +2141,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2138,39 +2185,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -2189,39 +2236,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -2233,40 +2280,40 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -2285,39 +2332,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2329,39 +2376,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -2380,39 +2427,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -2444,39 +2491,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -2503,39 +2550,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -2547,39 +2594,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -2592,39 +2639,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -2633,39 +2680,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2683,39 +2730,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2741,39 +2788,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2793,40 +2840,40 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2842,39 +2889,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2894,39 +2941,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2952,39 +2999,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3000,39 +3047,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3053,39 +3100,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -3099,40 +3146,40 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -3148,39 +3195,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3200,39 +3247,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -3246,39 +3293,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3298,39 +3345,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3347,39 +3394,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -3402,39 +3449,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3454,39 +3501,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3503,39 +3550,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3552,39 +3599,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -3599,39 +3646,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3655,39 +3702,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -3710,39 +3757,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3760,39 +3807,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3810,39 +3857,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3862,39 +3909,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3912,39 +3959,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3962,39 +4009,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4012,39 +4059,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -4059,39 +4106,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4109,39 +4156,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -4159,39 +4206,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4209,39 +4256,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4256,39 +4303,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4303,39 +4350,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4350,39 +4397,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4401,40 +4448,40 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -4453,39 +4500,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4495,39 +4542,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4545,39 +4592,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4593,39 +4640,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4644,39 +4691,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4694,39 +4741,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -4748,39 +4795,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -4803,39 +4850,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -4845,39 +4892,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -4887,39 +4934,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -4949,39 +4996,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -4999,39 +5046,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5048,39 +5095,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5096,39 +5143,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -5157,39 +5204,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -5210,39 +5257,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5257,39 +5304,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5303,40 +5350,40 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5352,39 +5399,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5400,39 +5447,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5448,39 +5495,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5496,40 +5543,40 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5545,39 +5592,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5595,39 +5642,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -5643,39 +5690,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5690,39 +5737,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -5737,39 +5784,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5790,40 +5837,40 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -5838,39 +5885,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -5891,39 +5938,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -5956,39 +6003,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6004,39 +6051,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6052,39 +6099,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6102,39 +6149,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6151,39 +6198,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -6207,39 +6254,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6254,39 +6301,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6302,39 +6349,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6351,40 +6398,40 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6400,39 +6447,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -6452,39 +6499,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6500,40 +6547,40 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6549,39 +6596,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6602,39 +6649,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6657,39 +6704,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6710,39 +6757,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6766,39 +6813,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6821,39 +6868,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6876,39 +6923,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6930,39 +6977,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -6992,39 +7039,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7040,39 +7087,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7088,40 +7135,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7140,40 +7187,40 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7191,39 +7238,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
